--- a/templates/000_pm_suite/02_프로젝트 개발/01_컨설팅/02_제안작업/견적서 샘플.xlsx
+++ b/templates/000_pm_suite/02_프로젝트 개발/01_컨설팅/02_제안작업/견적서 샘플.xlsx
@@ -25,25 +25,25 @@
     <t>견적일 : 2022. 05. 24.</t>
   </si>
   <si>
-    <t>㈜주식회사 엠파시</t>
+    <t>주식회사 엠파시</t>
   </si>
   <si>
     <t>아래와 같이 견적 합니다.</t>
   </si>
   <si>
-    <t>서울시 금천구 가산디지털2로173</t>
+    <t>서울특별시 금천구 가산디지털1로 205-27</t>
   </si>
   <si>
     <t>견적유효기간을 견적일로부터 1개월입니다.</t>
   </si>
   <si>
-    <t>에이스비즈포레 603호</t>
+    <t>2층 208호 (가산동)</t>
   </si>
   <si>
     <t>대표이사 이 호 영     (인)</t>
   </si>
   <si>
-    <t>Tel:02-3489-1115, Fax:02-3489-1116</t>
+    <t>Tel: 0507-1360-8169, Email: poh@empasy.com</t>
   </si>
   <si>
     <t>(단위 : 원)</t>

--- a/templates/000_pm_suite/02_프로젝트 개발/01_컨설팅/02_제안작업/견적서 샘플.xlsx
+++ b/templates/000_pm_suite/02_프로젝트 개발/01_컨설팅/02_제안작업/견적서 샘플.xlsx
@@ -556,7 +556,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>[PM-29] 한빛글로벌 SyncGuard AI 시스템 구축 공식 견적서 — 주식회사 한빛글로벌 SyncGuard AI 시스템 구축</t>
+          <t>[PM-29] 한빛글로벌 SyncFlow AI 시스템 구축 공식 견적서 — 주식회사 한빛글로벌 SyncFlow AI 시스템 구축</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>세부 과업 및 산출 내역 (SyncGuard AI 구축)</t>
+          <t>세부 과업 및 산출 내역 (SyncFlow AI 구축)</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>HB-SSO, MarketingHub API, ProductLab 일배치 어댑터</t>
+          <t>HB-SSO, SRM-Portal API, PLM-Nexus 일배치 어댑터</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr">
